--- a/data/trans_dic/IP1001-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1001-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen asma</t>
+          <t>Menores que padecen asma (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -716,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,19</t>
+          <t>0,99; 8,1</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>0,0; 6,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 9,99</t>
+          <t>1,11; 10,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,51</t>
+          <t>0,0; 4,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,21</t>
+          <t>0,0; 8,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,91; 8,19</t>
+          <t>0,9; 8,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -751,34 +752,34 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,93; 5,72</t>
+          <t>0,94; 5,86</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 5,3</t>
+          <t>0,51; 4,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,23; 7,02</t>
+          <t>1,19; 6,8</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,97</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,81</t>
+          <t>1,28; 8,82</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,66; 7,23</t>
+          <t>0,88; 6,95</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 6,08</t>
+          <t>0,63; 5,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 6,93</t>
+          <t>0,76; 7,11</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,14</t>
+          <t>1,19; 7,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,75</t>
+          <t>1,68; 9,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,16</t>
+          <t>0,63; 5,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,82; 6,21</t>
+          <t>1,9; 6,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 6,79</t>
+          <t>1,93; 6,68</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 4,14</t>
+          <t>0,95; 4,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,47</t>
+          <t>0,56; 3,43</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,14</t>
+          <t>0,0; 4,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,27</t>
+          <t>0,99; 8,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,81</t>
+          <t>0,0; 7,88</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,99</t>
+          <t>0,0; 6,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,67</t>
+          <t>0,91; 7,62</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,75</t>
+          <t>0,0; 4,23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 17,23</t>
+          <t>3,86; 16,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,7</t>
+          <t>0,44; 3,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,99</t>
+          <t>1,01; 6,02</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,54; 4,48</t>
+          <t>0,53; 5,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,1; 9,29</t>
+          <t>1,71; 9,25</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,07; 9,28</t>
+          <t>0,74; 8,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 8,21</t>
+          <t>0,79; 8,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,24; 10,29</t>
+          <t>2,23; 10,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 9,44</t>
+          <t>1,04; 8,22</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,17</t>
+          <t>0,76; 7,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,4; 12,62</t>
+          <t>3,1; 12,31</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 7,24</t>
+          <t>1,69; 6,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,71</t>
+          <t>1,27; 6,21</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 9,57</t>
+          <t>3,11; 9,61</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,18</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,58; 19,95</t>
+          <t>3,24; 19,31</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,76; 16,76</t>
+          <t>2,13; 17,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,32</t>
+          <t>0,0; 11,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 12,69</t>
+          <t>1,49; 11,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,97</t>
+          <t>0,0; 7,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,29</t>
+          <t>0,0; 10,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,26; 13,2</t>
+          <t>3,23; 12,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,68; 9,17</t>
+          <t>1,66; 10,0</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,89; 7,78</t>
+          <t>0,95; 7,87</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0; 1,37</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,72</t>
+          <t>1,12; 9,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,87</t>
+          <t>0,0; 10,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,03</t>
+          <t>0,0; 9,1</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 9,35</t>
+          <t>0,96; 9,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,42</t>
+          <t>0,0; 7,23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,67; 11,92</t>
+          <t>1,61; 10,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 7,1</t>
+          <t>1,18; 6,77</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 3,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,45</t>
+          <t>0,0; 5,15</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 8,33</t>
+          <t>1,76; 8,13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,33</t>
+          <t>0,53; 4,45</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 3,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,0; 3,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,84; 10,2</t>
+          <t>2,9; 9,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,35</t>
+          <t>0,0; 2,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,16</t>
+          <t>0,42; 4,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,63; 17,32</t>
+          <t>5,32; 17,55</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,85</t>
+          <t>0,51; 2,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,01</t>
+          <t>0,23; 1,95</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,56</t>
+          <t>0,44; 2,77</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 13,59</t>
+          <t>5,45; 13,08</t>
         </is>
       </c>
     </row>
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,7; 4,66</t>
+          <t>0,77; 4,55</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,87</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,0; 2,56</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,0; 3,53</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,46; 5,93</t>
+          <t>1,43; 5,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,62; 6,57</t>
+          <t>1,97; 6,89</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,49; 5,93</t>
+          <t>1,52; 5,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,72</t>
+          <t>0,46; 4,62</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,39; 4,23</t>
+          <t>1,35; 4,17</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,69</t>
+          <t>1,06; 3,71</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,56</t>
+          <t>1,02; 3,52</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 3,03</t>
+          <t>0,5; 2,73</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,27</t>
+          <t>2,04; 4,13</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,88</t>
+          <t>1,2; 2,94</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,42; 3,3</t>
+          <t>1,48; 3,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,39</t>
+          <t>1,31; 3,3</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,86; 3,78</t>
+          <t>1,83; 3,76</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,86</t>
+          <t>1,87; 3,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,74</t>
+          <t>1,71; 3,59</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,29; 5,44</t>
+          <t>2,26; 5,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,2; 3,63</t>
+          <t>2,18; 3,59</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,09</t>
+          <t>1,7; 3,04</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,2</t>
+          <t>1,8; 3,17</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,13; 3,91</t>
+          <t>2,12; 3,97</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen asma (tasa de respuesta: 99,83%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1590</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>568</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2206</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1847</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1843</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3005</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>2415</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4049</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>519; 4257</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3428</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>636; 6264</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3582</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4973</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>554; 4997</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>556; 4868</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1056; 6607</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>588; 5427</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1455; 8288</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3849</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>4147</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2930</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2592</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3775</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3471</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4929</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2149</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>7618</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7859</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>4742</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3775</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1300; 8954</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>917; 7273</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>654; 5859</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>969; 9024</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1295; 8169</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1868; 10653</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>696; 6471</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>3996; 13299</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>4160; 14418</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2033; 9563</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1437; 8719</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>691</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2139</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1518</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1224</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>5796</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1914</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4148</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>2252</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>5796</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3154</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>676; 5845</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5264</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4308</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>645; 5375</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2955</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2591; 11408</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>609; 5187</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>1402; 8353</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>731; 6858</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>2147; 11608</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2742</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2557</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>3751</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2147</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5655</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>5575</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4704</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>9406</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>552; 6602</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>615; 6955</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1714; 7787</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>821; 6506</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>627; 5784</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2520; 9994</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>2598; 10747</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2026; 9942</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>4918; 15204</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>4063</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3297</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>1393</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>6157</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3967</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2842</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1357; 8083</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>933; 7653</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5166</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>668; 4989</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3427</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4799</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2800; 10741</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1494; 9001</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>856; 7063</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>2034</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1678</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1364</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>1841</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1428</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2816</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>3875</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>1428</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1678</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4180</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>626; 5507</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5942</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4201</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>571; 5518</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4358</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>906; 6083</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1369; 7834</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4392</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>0; 5765</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>1806; 8320</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2131</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1349</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1316</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>7427</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>2081</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>15544</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3425</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>22971</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>685; 5729</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4710</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4334</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>3606; 12362</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3887</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3350</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>611; 6062</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>8307; 27373</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1337; 7428</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>648; 5547</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>1235; 7801</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>15288; 36680</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>3137</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1252</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>5105</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>6337</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>3004</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>8242</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>6946</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>6649</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>3758</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1217; 7188</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 2935</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4201</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4651</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>2346; 9748</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>3374; 11799</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>2603; 10189</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>727; 7238</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>4360; 13423</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>3567; 12471</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3418; 11791</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>1453; 7876</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>20535</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>13448</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>15761</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>14095</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>19277</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>20013</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>19253</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>27160</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>39811</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>33461</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>35014</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>41255</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>13883; 28151</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>8489; 20761</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>10432; 24039</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>8708; 21961</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>13233; 27208</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>14034; 28950</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>12716; 26725</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>17244; 40171</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>30612; 50416</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>24805; 44239</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>26154; 46007</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>30329; 56621</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1001-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1001-Provincia-trans_dic.xlsx
@@ -717,37 +717,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,99; 8,1</t>
+          <t>0,98; 8,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,47</t>
+          <t>0,0; 5,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 10,92</t>
+          <t>1,11; 10,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,89</t>
+          <t>0,0; 5,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,26</t>
+          <t>0,0; 8,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,14</t>
+          <t>0,9; 8,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,55</t>
+          <t>0,86; 7,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,22 +757,22 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,86</t>
+          <t>0,94; 5,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,51; 4,75</t>
+          <t>0,54; 5,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,8</t>
+          <t>1,34; 6,86</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,52</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
     </row>
@@ -857,37 +857,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,28; 8,82</t>
+          <t>1,26; 8,38</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 6,95</t>
+          <t>0,67; 7,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,64</t>
+          <t>0,64; 5,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,11</t>
+          <t>0,68; 6,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 7,51</t>
+          <t>1,2; 7,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 9,58</t>
+          <t>1,71; 8,83</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,87</t>
+          <t>0,63; 5,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,22 +897,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 6,32</t>
+          <t>1,96; 6,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,93; 6,68</t>
+          <t>1,92; 6,78</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,46</t>
+          <t>0,92; 4,25</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,43</t>
+          <t>0,36; 3,3</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,67</t>
+          <t>0,0; 5,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 8,57</t>
+          <t>1,0; 8,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1017,42 +1017,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,13</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 7,62</t>
+          <t>0,91; 7,63</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,23</t>
+          <t>0,0; 5,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 16,99</t>
+          <t>3,8; 17,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,76</t>
+          <t>0,44; 4,1</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 6,02</t>
+          <t>1,44; 6,49</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,02</t>
+          <t>0,53; 4,46</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,71; 9,25</t>
+          <t>1,94; 9,86</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 8,82</t>
+          <t>1,4; 9,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 8,94</t>
+          <t>1,12; 8,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,23; 10,12</t>
+          <t>1,82; 10,01</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,04; 8,22</t>
+          <t>1,02; 9,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 7,03</t>
+          <t>0,77; 7,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 12,31</t>
+          <t>3,32; 13,2</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,98</t>
+          <t>1,5; 6,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,27; 6,21</t>
+          <t>1,35; 5,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,11; 9,61</t>
+          <t>3,27; 9,22</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,24; 19,31</t>
+          <t>4,57; 19,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 17,43</t>
+          <t>2,06; 17,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,89</t>
+          <t>0,0; 10,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,17 +1297,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,49; 11,12</t>
+          <t>1,48; 11,77</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,43</t>
+          <t>0,0; 7,46</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,35</t>
+          <t>0,0; 9,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 12,39</t>
+          <t>3,88; 12,94</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 10,0</t>
+          <t>1,73; 9,69</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,95; 7,87</t>
+          <t>0,69; 7,42</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 9,82</t>
+          <t>1,12; 10,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1427,22 +1427,22 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,95</t>
+          <t>0,0; 10,8</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,1</t>
+          <t>0,0; 9,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 9,24</t>
+          <t>0,96; 8,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,23</t>
+          <t>0,0; 7,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,27 +1452,27 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,61; 10,83</t>
+          <t>1,58; 11,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,77</t>
+          <t>1,52; 6,8</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,78</t>
+          <t>0,0; 3,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,15</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 8,13</t>
+          <t>1,67; 7,71</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,45</t>
+          <t>0,53; 4,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,4</t>
+          <t>0,0; 3,43</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,16</t>
+          <t>0,0; 3,46</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,9; 9,93</t>
+          <t>3,0; 10,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,87</t>
+          <t>0,0; 2,88</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,25</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 4,21</t>
+          <t>0,42; 3,92</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,32; 17,55</t>
+          <t>5,72; 17,23</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,81</t>
+          <t>0,51; 2,89</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,95</t>
+          <t>0,23; 1,9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,44; 2,77</t>
+          <t>0,42; 2,88</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,45; 13,08</t>
+          <t>5,09; 12,84</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,55</t>
+          <t>0,69; 4,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 2,4</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,56</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,53</t>
+          <t>0,0; 2,35</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,43; 5,94</t>
+          <t>1,45; 5,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,97; 6,89</t>
+          <t>1,92; 6,77</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,52; 5,96</t>
+          <t>1,45; 6,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,62</t>
+          <t>0,47; 4,44</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,17</t>
+          <t>1,43; 4,42</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,71</t>
+          <t>1,04; 3,51</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,02; 3,52</t>
+          <t>1,05; 3,63</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,73</t>
+          <t>0,5; 2,84</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,04; 4,13</t>
+          <t>2,15; 4,26</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,2; 2,94</t>
+          <t>1,11; 2,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,48; 3,41</t>
+          <t>1,49; 3,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,3</t>
+          <t>1,31; 3,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,76</t>
+          <t>1,81; 3,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,87; 3,87</t>
+          <t>1,79; 3,85</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,71; 3,59</t>
+          <t>1,79; 3,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,27</t>
+          <t>2,46; 5,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,59</t>
+          <t>2,19; 3,59</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,04</t>
+          <t>1,69; 3,03</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,8; 3,17</t>
+          <t>1,78; 3,1</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,97</t>
+          <t>2,16; 4,07</t>
         </is>
       </c>
     </row>
@@ -2209,37 +2209,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>519; 4257</t>
+          <t>518; 4275</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3428</t>
+          <t>0; 3034</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>636; 6264</t>
+          <t>635; 6069</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3582</t>
+          <t>0; 4038</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4973</t>
+          <t>0; 4904</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>554; 4997</t>
+          <t>553; 5010</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>556; 4868</t>
+          <t>556; 4971</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,22 +2249,22 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1056; 6607</t>
+          <t>1061; 6632</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>588; 5427</t>
+          <t>616; 6059</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1455; 8288</t>
+          <t>1634; 8362</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3849</t>
+          <t>0; 4002</t>
         </is>
       </c>
     </row>
@@ -2417,37 +2417,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1300; 8954</t>
+          <t>1284; 8514</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>917; 7273</t>
+          <t>702; 7504</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>654; 5859</t>
+          <t>662; 6014</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>969; 9024</t>
+          <t>859; 8866</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1295; 8169</t>
+          <t>1300; 8313</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1868; 10653</t>
+          <t>1904; 9821</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>696; 6471</t>
+          <t>690; 5751</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2457,22 +2457,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3996; 13299</t>
+          <t>4122; 13270</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4160; 14418</t>
+          <t>4152; 14636</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2033; 9563</t>
+          <t>1966; 9111</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1437; 8719</t>
+          <t>922; 8399</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3154</t>
+          <t>0; 3446</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>676; 5845</t>
+          <t>679; 5704</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2645,42 +2645,42 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4308</t>
+          <t>0; 3804</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>645; 5375</t>
+          <t>642; 5382</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2955</t>
+          <t>0; 3663</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2591; 11408</t>
+          <t>2552; 11576</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>609; 5187</t>
+          <t>607; 5659</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1402; 8353</t>
+          <t>1995; 8999</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>731; 6858</t>
+          <t>729; 6101</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2147; 11608</t>
+          <t>2438; 12372</t>
         </is>
       </c>
     </row>
@@ -2833,17 +2833,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>552; 6602</t>
+          <t>1049; 7198</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>615; 6955</t>
+          <t>873; 6736</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1714; 7787</t>
+          <t>1400; 7705</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2853,17 +2853,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>821; 6506</t>
+          <t>810; 7608</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>627; 5784</t>
+          <t>636; 6495</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2520; 9994</t>
+          <t>2698; 10719</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2598; 10747</t>
+          <t>2309; 10284</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026; 9942</t>
+          <t>2153; 9582</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4918; 15204</t>
+          <t>5170; 14582</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1357; 8083</t>
+          <t>1915; 8231</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>933; 7653</t>
+          <t>904; 7475</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5166</t>
+          <t>0; 4751</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,17 +3061,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>668; 4989</t>
+          <t>664; 5279</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3427</t>
+          <t>0; 3440</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4799</t>
+          <t>0; 4590</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2800; 10741</t>
+          <t>3367; 11217</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1494; 9001</t>
+          <t>1553; 8718</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>856; 7063</t>
+          <t>617; 6665</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>626; 5507</t>
+          <t>626; 5865</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -3259,22 +3259,22 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5942</t>
+          <t>0; 5859</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4201</t>
+          <t>0; 4156</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>571; 5518</t>
+          <t>573; 4999</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4358</t>
+          <t>0; 4296</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3284,27 +3284,27 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>906; 6083</t>
+          <t>889; 6185</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1369; 7834</t>
+          <t>1757; 7877</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4392</t>
+          <t>0; 4373</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5765</t>
+          <t>0; 5619</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1806; 8320</t>
+          <t>1707; 7895</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>685; 5729</t>
+          <t>686; 5733</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4710</t>
+          <t>0; 4757</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4334</t>
+          <t>0; 4748</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3606; 12362</t>
+          <t>3740; 13556</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3887</t>
+          <t>0; 3910</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3350</t>
+          <t>0; 3277</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>611; 6062</t>
+          <t>607; 5643</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8307; 27373</t>
+          <t>8920; 26873</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1337; 7428</t>
+          <t>1339; 7633</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>648; 5547</t>
+          <t>647; 5399</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1235; 7801</t>
+          <t>1174; 8116</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>15288; 36680</t>
+          <t>14292; 36006</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1217; 7188</t>
+          <t>1094; 7096</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 2935</t>
+          <t>0; 3952</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4201</t>
+          <t>0; 3808</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 4651</t>
+          <t>0; 3090</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2346; 9748</t>
+          <t>2379; 9491</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3374; 11799</t>
+          <t>3293; 11606</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2603; 10189</t>
+          <t>2483; 10659</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>727; 7238</t>
+          <t>732; 6965</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4360; 13423</t>
+          <t>4605; 14242</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3567; 12471</t>
+          <t>3482; 11781</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3418; 11791</t>
+          <t>3511; 12155</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1453; 7876</t>
+          <t>1436; 8182</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>13883; 28151</t>
+          <t>14626; 28995</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>8489; 20761</t>
+          <t>7856; 20292</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10432; 24039</t>
+          <t>10516; 23805</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8708; 21961</t>
+          <t>8724; 21433</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>13233; 27208</t>
+          <t>13052; 27270</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>14034; 28950</t>
+          <t>13431; 28854</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>12716; 26725</t>
+          <t>13327; 27885</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>17244; 40171</t>
+          <t>18728; 41195</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>30612; 50416</t>
+          <t>30674; 50444</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24805; 44239</t>
+          <t>24619; 44180</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>26154; 46007</t>
+          <t>25800; 44912</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>30329; 56621</t>
+          <t>30855; 58133</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1001-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/IP1001-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2,86%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3,03%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1,07%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3,84%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,35%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,98; 8,13</t>
+          <t>0,0; 8,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,73</t>
+          <t>0,91; 8,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 10,58</t>
+          <t>0,86; 7,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,14</t>
+          <t>0,98; 8,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,9; 8,16</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,86; 7,71</t>
+          <t>1,11; 9,99</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,94; 5,88</t>
+          <t>0,93; 5,72</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,54; 5,3</t>
+          <t>0,51; 5,3</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,86</t>
+          <t>1,23; 7,02</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,62</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,19%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,08%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,8%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>2,49%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,26; 8,38</t>
+          <t>1,19; 7,14</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 7,17</t>
+          <t>1,62; 8,75</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 5,79</t>
+          <t>0,62; 5,16</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 6,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,64</t>
+          <t>1,59; 8,81</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 8,83</t>
+          <t>0,66; 7,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 5,22</t>
+          <t>0,62; 6,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,29; 9,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,96; 6,31</t>
+          <t>1,82; 6,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,78</t>
+          <t>1,87; 6,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,25</t>
+          <t>0,93; 4,14</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,3</t>
+          <t>0,6; 4,22</t>
         </is>
       </c>
     </row>
@@ -929,44 +929,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2,85%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,05%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>7,95%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,14%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2,27%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>2,85%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>8,63%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>1,39%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,1</t>
+          <t>0,0; 6,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,0; 8,37</t>
+          <t>0,91; 7,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,88</t>
+          <t>0,0; 5,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
+          <t>3,75; 16,76</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 5,14</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,98; 8,27</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 7,81</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,41</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,91; 7,63</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 5,24</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>3,8; 17,24</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,44; 4,1</t>
+          <t>0,44; 3,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,44; 6,49</t>
+          <t>1,01; 5,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,46</t>
+          <t>0,54; 4,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 9,86</t>
+          <t>1,87; 7,82</t>
         </is>
       </c>
     </row>
@@ -1069,37 +1069,37 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,58%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6,97%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>3,66%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3,29%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>4,87%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,4; 9,62</t>
+          <t>1,04; 9,44</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,12; 8,66</t>
+          <t>0,77; 7,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,82; 10,01</t>
+          <t>3,4; 12,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,17 +1157,17 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,02; 9,62</t>
+          <t>1,07; 9,28</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,9</t>
+          <t>1,12; 8,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 13,2</t>
+          <t>2,24; 10,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1177,17 +1177,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,68</t>
+          <t>1,73; 7,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,35; 5,99</t>
+          <t>1,19; 5,71</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3,27; 9,22</t>
+          <t>3,32; 9,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1209,37 +1209,37 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>4,67%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,45%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>9,71%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>7,51%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>3,34%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>1,45%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 19,67</t>
+          <t>1,49; 12,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 17,03</t>
+          <t>0,0; 5,97</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,94</t>
+          <t>0,0; 9,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,17 +1297,17 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 11,77</t>
+          <t>4,58; 19,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,46</t>
+          <t>1,76; 16,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,9</t>
+          <t>0,0; 12,32</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,17 +1317,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,88; 12,94</t>
+          <t>3,26; 13,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 9,69</t>
+          <t>1,68; 9,17</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,69; 7,42</t>
+          <t>0,89; 7,78</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3,08%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2,37%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>3,63%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3,09%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,12; 10,46</t>
+          <t>0,95; 9,35</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>0,0; 7,42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 10,8</t>
-        </is>
-      </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,0</t>
+          <t>1,69; 12,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,37</t>
+          <t>1,12; 9,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,87</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>1,58; 11,01</t>
+          <t>0,0; 8,91</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,52; 6,8</t>
+          <t>1,55; 7,1</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,76</t>
+          <t>0,0; 3,93</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,02</t>
+          <t>0,0; 5,45</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,71</t>
+          <t>1,69; 8,4</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9,33%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1,66%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>0,97%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>0,96%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>5,96%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,44%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 4,46</t>
+          <t>0,0; 3,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 2,52</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,46</t>
+          <t>0,42; 4,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,0; 10,89</t>
+          <t>5,16; 14,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,88</t>
+          <t>0,53; 4,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,25</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,92</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,72; 17,23</t>
+          <t>3,05; 11,02</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,89</t>
+          <t>0,51; 2,85</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,9</t>
+          <t>0,23; 2,01</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,88</t>
+          <t>0,46; 2,56</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,09; 12,84</t>
+          <t>5,2; 11,93</t>
         </is>
       </c>
     </row>
@@ -1629,42 +1629,42 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3,11%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3,16%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>1,99%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>0,37%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>0,76%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,11%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,7%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>3,16%</t>
-        </is>
-      </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,33%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 4,49</t>
+          <t>1,46; 5,93</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>1,62; 6,57</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>1,49; 5,93</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,35</t>
+          <t>0,54; 4,86</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,79</t>
+          <t>0,7; 4,66</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,92; 6,77</t>
+          <t>0,0; 1,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,45; 6,24</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,44</t>
+          <t>0,0; 3,09</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,43; 4,42</t>
+          <t>1,39; 4,23</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,51</t>
+          <t>1,06; 3,69</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1,05; 3,63</t>
+          <t>0,93; 3,56</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,84</t>
+          <t>0,51; 3,12</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3,36%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1,9%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>2,24%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2,12%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,26</t>
+          <t>1,86; 3,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,11; 2,87</t>
+          <t>1,81; 3,86</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,38</t>
+          <t>1,75; 3,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1,31; 3,22</t>
+          <t>2,29; 4,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,81; 3,77</t>
+          <t>2,1; 4,27</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,85</t>
+          <t>1,16; 2,88</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>1,79; 3,74</t>
+          <t>1,42; 3,3</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2,46; 5,41</t>
+          <t>1,47; 3,75</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,59</t>
+          <t>2,2; 3,63</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 3,03</t>
+          <t>1,69; 3,09</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1,78; 3,1</t>
+          <t>1,82; 3,2</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,07</t>
+          <t>2,13; 3,77</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,42 +2073,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -2141,42 +2141,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>1415</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1847</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1843</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1590</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>568</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>2206</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>775</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1415</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1847</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1843</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>701</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>701</t>
         </is>
       </c>
     </row>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>518; 4275</t>
+          <t>0; 4947</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3034</t>
+          <t>560; 5025</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635; 6069</t>
+          <t>552; 4867</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4038</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4904</t>
+          <t>513; 4305</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>553; 5010</t>
+          <t>0; 2864</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>556; 4971</t>
+          <t>638; 5732</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3505</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1061; 6632</t>
+          <t>1053; 6450</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>616; 6059</t>
+          <t>586; 6057</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1634; 8362</t>
+          <t>1495; 8549</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4002</t>
+          <t>0; 4145</t>
         </is>
       </c>
     </row>
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3471</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4929</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2149</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>4147</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2930</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2592</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3775</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3471</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4929</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>2149</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3852</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1284; 8514</t>
+          <t>1294; 7761</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>702; 7504</t>
+          <t>1797; 9725</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>662; 6014</t>
+          <t>686; 5685</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>859; 8866</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1300; 8313</t>
+          <t>1613; 8947</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1904; 9821</t>
+          <t>695; 7571</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>690; 5751</t>
+          <t>645; 6317</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1301; 9060</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>4122; 13270</t>
+          <t>3827; 13071</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4152; 14636</t>
+          <t>4040; 14655</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1966; 9111</t>
+          <t>1989; 8862</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>922; 8399</t>
+          <t>1295; 9132</t>
         </is>
       </c>
     </row>
@@ -2489,42 +2489,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,44 +2557,44 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1224</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>4719</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>691</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>2139</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>1518</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="J11" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2009</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>734</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>5796</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
           <t>1914</t>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5796</t>
+          <t>4719</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3446</t>
+          <t>0; 4919</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>679; 5704</t>
+          <t>645; 5411</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 5264</t>
+          <t>0; 4017</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
+          <t>2225; 9949</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3473</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>668; 5639</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5218</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3804</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>642; 5382</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3663</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>2552; 11576</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>607; 5659</t>
+          <t>607; 5100</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1995; 8999</t>
+          <t>1403; 8305</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>729; 6101</t>
+          <t>735; 6128</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2438; 12372</t>
+          <t>2165; 9069</t>
         </is>
       </c>
     </row>
@@ -2702,32 +2702,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -2765,37 +2765,37 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2147</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5655</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>2742</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2557</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>3751</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2147</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5655</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -2833,17 +2833,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1049; 7198</t>
+          <t>821; 7469</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>873; 6736</t>
+          <t>630; 5900</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1400; 7705</t>
+          <t>2764; 10244</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2853,17 +2853,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>810; 7608</t>
+          <t>801; 6945</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>636; 6495</t>
+          <t>870; 6387</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2698; 10719</t>
+          <t>1720; 7921</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2873,17 +2873,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2309; 10284</t>
+          <t>2663; 11150</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2153; 9582</t>
+          <t>1897; 9133</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>5170; 14582</t>
+          <t>5257; 15133</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2905,32 +2905,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2973,37 +2973,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1393</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>4063</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>3297</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>1449</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2095</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>670</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>1393</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1915; 8231</t>
+          <t>670; 5689</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>904; 7475</t>
+          <t>0; 2750</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4751</t>
+          <t>0; 4306</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,17 +3061,17 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>664; 5279</t>
+          <t>1917; 8349</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3440</t>
+          <t>775; 7358</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 4590</t>
+          <t>0; 5352</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3367; 11217</t>
+          <t>2829; 11440</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1553; 8718</t>
+          <t>1509; 8256</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>617; 6665</t>
+          <t>798; 6990</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -3118,37 +3118,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3181,54 +3181,54 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1841</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1428</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2566</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>2034</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1678</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1364</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>1841</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1343</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>3875</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>1428</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>2816</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3875</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1428</t>
-        </is>
-      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
           <t>1678</t>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4180</t>
+          <t>3909</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>626; 5865</t>
+          <t>569; 5585</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>0; 4469</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>0; 5859</t>
-        </is>
-      </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 4156</t>
+          <t>825; 6155</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>573; 4999</t>
+          <t>629; 5446</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 4296</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 6445</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>889; 6185</t>
+          <t>0; 4078</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1757; 7877</t>
+          <t>1791; 8225</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 4373</t>
+          <t>0; 4563</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 5619</t>
+          <t>0; 6100</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1707; 7895</t>
+          <t>1598; 7955</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>10</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1294</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2081</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>13184</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>2131</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>1349</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>1316</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>7427</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1294</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>2081</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>15544</t>
+          <t>7824</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>22971</t>
+          <t>21008</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>686; 5733</t>
+          <t>0; 4539</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4757</t>
+          <t>0; 3674</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 4748</t>
+          <t>606; 5988</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3740; 13556</t>
+          <t>7296; 20624</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3910</t>
+          <t>684; 5575</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3277</t>
+          <t>0; 4099</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>607; 5643</t>
+          <t>0; 4297</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>8920; 26873</t>
+          <t>3742; 13501</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1339; 7633</t>
+          <t>1335; 7535</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>647; 5399</t>
+          <t>643; 5722</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1174; 8116</t>
+          <t>1304; 7197</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>14292; 36006</t>
+          <t>13716; 31478</t>
         </is>
       </c>
     </row>
@@ -3529,42 +3529,42 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>5105</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6337</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>3105</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>3137</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>609</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>1252</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>5105</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>6337</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>5398</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>3004</t>
+          <t>872</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>3758</t>
+          <t>3977</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1094; 7096</t>
+          <t>2398; 9727</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 3952</t>
+          <t>2777; 11253</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3808</t>
+          <t>2554; 10137</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0; 3090</t>
+          <t>857; 7744</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2379; 9491</t>
+          <t>1110; 7362</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3293; 11606</t>
+          <t>0; 3073</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2483; 10659</t>
+          <t>0; 4478</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>732; 6965</t>
+          <t>0; 4335</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>4605; 14242</t>
+          <t>4485; 13625</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>3482; 11781</t>
+          <t>3560; 12410</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>3511; 12155</t>
+          <t>3105; 11921</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>1436; 8182</t>
+          <t>1542; 9356</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>19</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>19277</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>20013</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>19253</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>23574</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>20535</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>13448</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>15761</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>14095</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>19277</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>20013</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>19253</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>27160</t>
+          <t>14592</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>41255</t>
+          <t>38166</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>14626; 28995</t>
+          <t>13421; 27329</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>7856; 20292</t>
+          <t>13587; 28897</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>10516; 23805</t>
+          <t>13025; 27863</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>8724; 21433</t>
+          <t>16067; 33293</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>13052; 27270</t>
+          <t>14301; 29054</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13431; 28854</t>
+          <t>8232; 20330</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13327; 27885</t>
+          <t>10036; 23232</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>18728; 41195</t>
+          <t>9262; 23575</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>30674; 50444</t>
+          <t>30919; 50899</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24619; 44180</t>
+          <t>24595; 44948</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25800; 44912</t>
+          <t>26405; 46378</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>30855; 58133</t>
+          <t>28380; 50180</t>
         </is>
       </c>
     </row>
